--- a/astro-site/public/dl/plan-negocio-finca-eventos-bodas/plan-financiero-finca-eventos-bodas.xlsx
+++ b/astro-site/public/dl/plan-negocio-finca-eventos-bodas/plan-financiero-finca-eventos-bodas.xlsx
@@ -1170,7 +1170,7 @@
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>El primer año sólo intereses: la primera temporada se vendió antes de tener la licencia y llega corta. Desde el segundo año se devuelve el principal: mira la holgura de caja de ese año en el Punto de Equilibrio</t>
+          <t>El primer año, sólo intereses: es el año de arranque y la caja va más justa. Desde el segundo año se devuelve el principal: mira la holgura de caja de ese año en el Punto de Equilibrio</t>
         </is>
       </c>
     </row>
@@ -1185,7 +1185,7 @@
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>Tres meses de costes fijos: son el colchón del primer invierno. En un año normal, de noviembre a febrero entra alrededor del 23 % de la venta con la renta y la plantilla planas</t>
+          <t>Tres meses de costes fijos: son el colchón de los primeros meses, recién pagada la inversión y antes de las bodas de mayo y junio. En un año normal, de noviembre a febrero entra alrededor del 23 % de la venta con la renta y la plantilla planas: ese invierno se pasa con la caja de la temporada</t>
         </is>
       </c>
     </row>
@@ -1237,7 +1237,7 @@
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>Tipo reducido de hostelería</t>
+          <t>No se usa en este plan: la finca no vende comida ni bebida. Es el tipo del menú del catering</t>
         </is>
       </c>
     </row>
@@ -1252,7 +1252,7 @@
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>Tipo general. En este libro lo usan dos cosas: el IVA que soportas al comprar el alcohol (el proveedor lo factura al 21 %) y el que repercutes por el alcohol que sale por intermediarios (es una entrega de bienes). El alcohol servido en la finca va al reducido: su tipo está en el bloque de desglose del IVA. Suministros, equipamiento y servicios tienen su tipo en la celda de abajo. El libro manda al general sólo el alcohol: si compras refrescos, zumos y gaseosas con azúcares o edulcorantes añadidos, su factura también va al 21 % (art. 91.Uno.1.1.º de la Ley 37/1992)</t>
+          <t>Tipo general. En este plan es el de todo lo que factura la finca (espacio, servicios y canon) y el de casi todo lo que compra; suministros, equipamiento y servicios tienen su tipo en la celda de abajo. La finca no vende comida ni bebida: el menú y la barra los factura el catering, al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992)</t>
         </is>
       </c>
     </row>
@@ -1380,7 +1380,7 @@
       </c>
       <c r="C52" t="inlineStr">
         <is>
-          <t>Una finca que acaba de abrir no factura el primer mes lo que factura al año: las bodas se reservan con 12-18 meses de antelación y la primera temporada sólo trae lo que se vendió desde la licencia. Con 100 % se elimina la rampa</t>
+          <t>Una finca que acaba de abrir no factura el primer mes lo que factura al año: las bodas se reservan con 12-18 meses de antelación y la primera temporada sólo trae lo que se reservó, condicionado a la licencia, durante la tramitación y la obra. Con 100 % se elimina la rampa</t>
         </is>
       </c>
     </row>
@@ -1759,7 +1759,7 @@
     <row r="8">
       <c r="A8" s="28" t="inlineStr">
         <is>
-          <t>Calificación urbanística, licencia, tasas y prestación compensatoria o canon</t>
+          <t>Licencias, tasas, calificación urbanística y prestación compensatoria o canon</t>
         </is>
       </c>
       <c r="B8" s="29" t="n">
@@ -1771,12 +1771,12 @@
       </c>
       <c r="D8" s="28" t="inlineStr">
         <is>
-          <t>Lo que cobra la administración en suelo rústico, distinto en cada comunidad: en Andalucía, prestación compensatoria del 10 % de las obras sin maquinaria (LISTA, art. 22.5); en la C. Valenciana, canon del 2 % (TRLOTUP, art. 221). Ajusta esta partida a la tuya: compruébalo en tu ayuntamiento y en tu comunidad</t>
+          <t>Lo que cobra la administración en suelo rústico, distinto en cada comunidad: en Andalucía, prestación compensatoria del 10 % de las obras sin maquinaria (LISTA, art. 22.5); en la C. Valenciana, canon del 2 % (TRLOTUP, art. 221). En Andalucía, sólo la prestación serían unos 13.000 € con la obra del caso: súbela si es tu comunidad. No lleva IVA. Ajusta esta partida a la tuya: compruébalo en tu ayuntamiento y en tu comunidad</t>
         </is>
       </c>
       <c r="E8" s="31" t="inlineStr">
         <is>
-          <t>Sí</t>
+          <t>No</t>
         </is>
       </c>
     </row>
@@ -1867,7 +1867,7 @@
       </c>
       <c r="D12" s="28" t="inlineStr">
         <is>
-          <t>Con un aseo adaptado e itinerario accesible: compruébalo con tu técnico sobre el Código Técnico</t>
+          <t>Con un aseo adaptado e itinerario accesible: compruébalo con tu técnico sobre el Código Técnico. Incluye la conexión al saneamiento (fosa séptica o depuradora); si hay que hacerla nueva o ampliarla para el aforo, súbela</t>
         </is>
       </c>
       <c r="E12" s="31" t="inlineStr">
@@ -1987,7 +1987,7 @@
       </c>
       <c r="D17" s="28" t="inlineStr">
         <is>
-          <t>Mesas redondas e imperiales, 250 sillas y mantelería base. La decoración especial la contratan los novios</t>
+          <t>Mesas redondas e imperiales, 300 sillas y mantelería base. La decoración especial la contratan los novios</t>
         </is>
       </c>
       <c r="E17" s="31" t="inlineStr">
@@ -2344,7 +2344,7 @@
       </c>
       <c r="B33" s="32">
         <f>IFERROR(IF(B31="","",SUMIF($E$7:$E$28,"Sí",$B$7:$B$28)*'0. Supuestos'!$B$41),"")</f>
-        <v>51193.799999999996</v>
+        <v>49093.799999999996</v>
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="str">
@@ -2361,7 +2361,7 @@
       </c>
       <c r="B34" s="26">
         <f>IFERROR(B31+B33,"")</f>
-        <v>362602.55</v>
+        <v>360502.55</v>
       </c>
       <c r="C34" s="28" t="n"/>
       <c r="D34" s="25" t="inlineStr">
@@ -2428,8 +2428,8 @@
       </c>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="25" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Calificación urbanística, licencia, tasas y prestación compensatoria o canon, Web, fotos, vídeo y marca, Constitución de la SL, Lanzamiento: feria nupcial, puertas abiertas y escaparate premium, Fianza del arrendamiento, Renta de la finca durante la obra ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B31-B36-B37,"0")&amp;" € de los "&amp;TEXT(B31,"0")&amp;" € de inversión.","")</f>
-        <v>No se amortizan, por no ser inmovilizado, Calificación urbanística, licencia, tasas y prestación compensatoria o canon, Web, fotos, vídeo y marca, Constitución de la SL, Lanzamiento: feria nupcial, puertas abiertas y escaparate premium, Fianza del arrendamiento, Renta de la finca durante la obra ni Colchón operativo hasta alcanzar el equilibrio. Suman 93129 € de los 311409 € de inversión.</v>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Licencias, tasas, calificación urbanística y prestación compensatoria o canon, Web, fotos, vídeo y marca, Constitución de la SL, Lanzamiento: feria nupcial, puertas abiertas y escaparate premium, Fianza del arrendamiento, Renta de la finca durante la obra ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B31-B36-B37,"0")&amp;" € de los "&amp;TEXT(B31,"0")&amp;" € de inversión.","")</f>
+        <v>No se amortizan, por no ser inmovilizado, Licencias, tasas, calificación urbanística y prestación compensatoria o canon, Web, fotos, vídeo y marca, Constitución de la SL, Lanzamiento: feria nupcial, puertas abiertas y escaparate premium, Fianza del arrendamiento, Renta de la finca durante la obra ni Colchón operativo hasta alcanzar el equilibrio. Suman 93129 € de los 311409 € de inversión.</v>
       </c>
       <c r="E38" s="28" t="n"/>
     </row>
@@ -5773,7 +5773,7 @@
       </c>
       <c r="J6" s="28" t="inlineStr">
         <is>
-          <t>Contrato fijo discontinuo (art. 16 del Estatuto de los Trabajadores) a jornada completa de marzo a noviembre: equivale al 75 % en cómputo anual. Prepara cada evento con los novios y el catering y lo dirige el día. Bruto a jornada completa: unos 1.650 €</t>
+          <t>Contrato fijo discontinuo (art. 16 del Estatuto de los Trabajadores) a jornada completa de marzo a noviembre: equivale al 75 % en cómputo anual. Prepara cada evento con los novios y el catering y lo dirige el día. De diciembre a febrero (comidas de Navidad y eventos de invierno) coordina el titular. Bruto a jornada completa: unos 1.650 €</t>
         </is>
       </c>
     </row>
@@ -6507,10 +6507,10 @@
       <c r="D11" s="28" t="n"/>
       <c r="E11" s="28" t="n"/>
     </row>
-    <row r="12" ht="45" customHeight="1">
+    <row r="12" ht="60" customHeight="1">
       <c r="A12" s="46" t="inlineStr">
         <is>
-          <t>8. El documento Word de este pack, la calculadora de presupuestos y los modelos de contrato usan las cifras de este Excel: si cambias una celda verde, el Excel manda.</t>
+          <t>8. El documento Word de este pack usa las cifras de este Excel; la calculadora de presupuestos y los modelos de contrato usan los mismos porcentajes de cobro y de cancelación. Si cambias una celda verde, el Excel manda.</t>
         </is>
       </c>
       <c r="B12" s="28" t="n"/>
@@ -6717,7 +6717,7 @@
       </c>
       <c r="B26" s="32">
         <f>IFERROR(IF('Inversión Inicial'!$B$34="","",'Inversión Inicial'!$B$34),"")</f>
-        <v>362602.55</v>
+        <v>360502.55</v>
       </c>
       <c r="C26" s="28" t="n"/>
       <c r="D26" s="28" t="n"/>
@@ -6834,7 +6834,7 @@
       </c>
       <c r="E34" s="28" t="n"/>
     </row>
-    <row r="35" ht="45" customHeight="1">
+    <row r="35" ht="60" customHeight="1">
       <c r="A35" s="28" t="inlineStr">
         <is>
           <t>Mes 1 del plan</t>
@@ -6852,7 +6852,7 @@
       </c>
       <c r="D35" s="46" t="inlineStr">
         <is>
-          <t>La obra y la licencia se hacen en otoño e invierno y se abre con las comuniones y la empresa de primavera. La fila de estacionalidad de la Tesorería ya va girada</t>
+          <t>La licencia (de 6 a 12 meses o más) y la obra se cierran durante el invierno anterior, y se abre con las comuniones y la empresa de primavera. La fila de estacionalidad de la Tesorería ya va girada</t>
         </is>
       </c>
       <c r="E35" s="28" t="n"/>
@@ -6898,7 +6898,7 @@
       </c>
       <c r="D37" s="46" t="inlineStr">
         <is>
-          <t>Las 30 bodas son unas 21 en sábados de temporada (el 80 %) y el resto en viernes, domingos o fuera de temporada. El libro no comprueba este techo: compruébalo tú en tu calendario</t>
+          <t>Las 30 bodas son unas 24 en sábados de temporada (el 80 %) y el resto en viernes, domingos o fuera de temporada. El libro no comprueba este techo: compruébalo tú en tu calendario</t>
         </is>
       </c>
       <c r="E37" s="28" t="n"/>
@@ -6926,7 +6926,7 @@
       </c>
       <c r="E38" s="28" t="n"/>
     </row>
-    <row r="39" ht="30" customHeight="1">
+    <row r="39" ht="45" customHeight="1">
       <c r="A39" s="28" t="inlineStr">
         <is>
           <t>Antelación de la reserva de una boda</t>
@@ -6944,7 +6944,7 @@
       </c>
       <c r="D39" s="46" t="inlineStr">
         <is>
-          <t>Por eso la primera temporada se vende antes de abrir y la rampa del plan dura 12 meses</t>
+          <t>Por eso la primera temporada se reserva antes de abrir, condicionada a la licencia, y la rampa del plan dura 12 meses</t>
         </is>
       </c>
       <c r="E39" s="28" t="n"/>
@@ -7013,7 +7013,7 @@
       </c>
       <c r="D42" s="46" t="inlineStr">
         <is>
-          <t>Boda: 2 auxiliares × 12 h · empresa 1 × 9 h · celebración 1 × 8 h · pequeño 1 × 5 h. Camareros y cocina los pone el catering</t>
+          <t>Boda: 2 auxiliares × 13 h · empresa 1 × 9 h · celebración 1 × 8 h · pequeño 1 × 5 h. Camareros y cocina los pone el catering</t>
         </is>
       </c>
       <c r="E42" s="28" t="n"/>
@@ -7049,7 +7049,7 @@
       </c>
       <c r="B44" s="28" t="inlineStr">
         <is>
-          <t>Desde 1.000 personas en edificio cerrado o carpa · 5.000 al aire libre</t>
+          <t>Desde 1.000 personas en edificio cerrado o carpa · 5.000 al aire libre en recinto delimitado</t>
         </is>
       </c>
       <c r="C44" s="28" t="inlineStr">
@@ -7569,7 +7569,7 @@
       </c>
       <c r="O5" s="28" t="inlineStr">
         <is>
-          <t>Mes 1 = MARZO: la obra y la licencia se hacen en otoño e invierno y se abre con las comuniones y la empresa de primavera. Los picos son junio (Mes 4) y septiembre (Mes 7); el valle, enero (Mes 11). Si abres en otro mes, gira la fila. Tiene que sumar 100 %</t>
+          <t>Mes 1 = MARZO: la licencia (de 6 a 12 meses o más) y la obra se cierran durante el invierno anterior, y se abre con las comuniones y la empresa de primavera. Los picos son junio (Mes 4) y septiembre (Mes 7); el valle, enero (Mes 11). Si abres en otro mes, gira la fila. Tiene que sumar 100 %</t>
         </is>
       </c>
     </row>
@@ -8175,7 +8175,7 @@
       </c>
       <c r="O16" s="28" t="inlineStr">
         <is>
-          <t>Cada línea de venta a SU tipo, leído de la columna de IVA del P&amp;L: en la finca, alcohol incluido, el reducido (art. 91.Uno.2.2.º de la Ley 37/1992 del IVA); el alcohol que sale por intermediarios, al general; el espacio, los servicios y el canon de la finca, al general (el 21 %)</t>
+          <t>Cada línea de venta a SU tipo, leído de la columna de IVA del P&amp;L: el espacio, los servicios y el canon de la finca, al general (21 %). La finca no vende comida ni bebida: el menú y la barra los factura el catering, al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992)</t>
         </is>
       </c>
     </row>
@@ -8254,19 +8254,19 @@
       <c r="D18" s="28" t="n"/>
       <c r="E18" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",'Inversión Inicial'!$B$33),"")</f>
-        <v>51193.799999999996</v>
+        <v>49093.799999999996</v>
       </c>
       <c r="F18" s="28" t="n"/>
       <c r="G18" s="28" t="n"/>
       <c r="H18" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",MAX(0,-E19)),"")</f>
-        <v>44383.703893850325</v>
+        <v>42283.703893850325</v>
       </c>
       <c r="I18" s="28" t="n"/>
       <c r="J18" s="28" t="n"/>
       <c r="K18" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",MAX(0,-H19)),"")</f>
-        <v>34768.260499648415</v>
+        <v>32668.260499648415</v>
       </c>
       <c r="L18" s="28" t="n"/>
       <c r="M18" s="28" t="n"/>
@@ -8288,19 +8288,19 @@
       <c r="D19" s="28" t="n"/>
       <c r="E19" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(B16:D16)-SUM(B17:D17)-E18),"")</f>
-        <v>-44383.703893850325</v>
+        <v>-42283.703893850325</v>
       </c>
       <c r="F19" s="28" t="n"/>
       <c r="G19" s="28" t="n"/>
       <c r="H19" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(E16:G16)-SUM(E17:G17)-H18),"")</f>
-        <v>-34768.260499648415</v>
+        <v>-32668.260499648415</v>
       </c>
       <c r="I19" s="28" t="n"/>
       <c r="J19" s="28" t="n"/>
       <c r="K19" s="32">
         <f>IFERROR(IF('PyG 3 Años'!$B$9="","",SUM(H16:J16)-SUM(H17:J17)-K18),"")</f>
-        <v>-18757.688927469615</v>
+        <v>-16657.688927469615</v>
       </c>
       <c r="L19" s="28" t="n"/>
       <c r="M19" s="28" t="n"/>
@@ -8758,7 +8758,7 @@
     <row r="34" ht="225" customHeight="1">
       <c r="A34" s="46" t="inlineStr">
         <is>
-          <t>Los trimestres de esta hoja son de tres meses del plan (marzo-mayo, junio-agosto y septiembre-noviembre), no los naturales: con el Mes 1 en marzo, el modelo 303 se presenta en abril (por marzo), julio, octubre y enero (por octubre-diciembre, ya en el Mes 11). En el caso todos los trimestres salen a compensar y la finca no paga IVA en su primer año: el de la obra se descuenta de lo que repercutes, y tras el tercer trimestre del plan aún quedan unos 18.760 € por compensar. El Impuesto de Sociedades del año 1 se paga en julio del año 2. La cuota del préstamo se reparte en doce partes iguales siguiendo el cuadro ANUAL de la hoja de Financiación, y las nóminas en doce mensualidades más las dos pagas extra en su mes.</t>
+          <t>Los trimestres de esta hoja son de tres meses del plan (marzo-mayo, junio-agosto y septiembre-noviembre), no los naturales: con el Mes 1 en marzo, el modelo 303 se presenta en abril (por marzo), julio, octubre y enero (por octubre-diciembre, ya en el Mes 11). En el caso todos los trimestres salen a compensar y la finca no paga IVA en su primer año: el de la obra se descuenta de lo que repercutes, y tras el tercer trimestre del plan aún quedan unos 16.660 € por compensar. El Impuesto de Sociedades del año 1 se paga en julio del año 2. La cuota del préstamo se reparte en doce partes iguales siguiendo el cuadro ANUAL de la hoja de Financiación, y las nóminas en doce mensualidades más las dos pagas extra en su mes.</t>
         </is>
       </c>
       <c r="B34" s="28" t="n"/>
@@ -9708,7 +9708,7 @@
       </c>
       <c r="B14" s="32">
         <f>IFERROR(IF('Inversión Inicial'!$B$34="","",'Inversión Inicial'!$B$34),"")</f>
-        <v>362602.55</v>
+        <v>360502.55</v>
       </c>
       <c r="C14" s="28" t="inlineStr">
         <is>
@@ -9729,7 +9729,7 @@
       </c>
       <c r="B15" s="26">
         <f>IFERROR(B12-B14,"")</f>
-        <v>397.45000000001164</v>
+        <v>2497.4500000000116</v>
       </c>
       <c r="C15" s="25" t="inlineStr">
         <is>
@@ -9750,7 +9750,7 @@
       </c>
       <c r="B16" s="67">
         <f>IFERROR(B15/B14,"")</f>
-        <v>0.0010961037091438315</v>
+        <v>0.006927690247960831</v>
       </c>
       <c r="C16" s="28" t="inlineStr">
         <is>
@@ -9791,7 +9791,7 @@
       </c>
       <c r="B18" s="32">
         <f>IFERROR(MAX(0,B14-B12+B7),"")</f>
-        <v>262602.55</v>
+        <v>260502.55</v>
       </c>
       <c r="C18" s="28" t="inlineStr">
         <is>

--- a/astro-site/public/dl/plan-negocio-finca-eventos-bodas/plan-financiero-finca-eventos-bodas.xlsx
+++ b/astro-site/public/dl/plan-negocio-finca-eventos-bodas/plan-financiero-finca-eventos-bodas.xlsx
@@ -826,7 +826,7 @@
         <v>44.769999999999996</v>
       </c>
       <c r="C9" t="str">
-        <f>IFERROR("Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: "&amp;TEXT(SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)*100,"0")&amp;" %. La finca factura el espacio, los servicios y el canon al 21 %, el tipo general; el menú y la barra los factura el catering a los novios, al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992), y no entran en este libro. Aquí va redondeado. Compáralo con el rango del sector, que va con IVA.","")</f>
+        <f>IFERROR("Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: "&amp;TEXT(SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)*100,"0")&amp;" %. La finca factura el espacio, los servicios y el canon al 21 %, el tipo general; el menú y la barra los factura el catering a los novios, al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992), y no entran en este libro. Aquí va redondeado. "&amp;"Compáralo con el rango del sector, que va con IVA.","")</f>
         <v>Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: 21 %. La finca factura el espacio, los servicios y el canon al 21 %, el tipo general; el menú y la barra los factura el catering a los novios, al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992), y no entran en este libro. Aquí va redondeado. Compáralo con el rango del sector, que va con IVA.</v>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
         <v>0.036222488931348266</v>
       </c>
       <c r="D28" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico y dirección de obra, Adecuación del salón: suelos, cerramientos, carpintería y pintura, Acústica y aislamiento del salón, Aseos: dos bloques y uno adaptado, Instalación eléctrica: cuadro, alumbrado exterior y de emergencia, Climatización del salón, Office del catering: cámara, fregaderos, mesas inox, agua y desagüe, Aparcamiento y caminos: zahorra, señalización e iluminación, Jardinería, paisajismo y riego inicial y Protección contra incendios, señalización de evacuación y accesibilidad), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico y dirección de obra, Adecuación del salón: suelos, cerramientos, carpintería y pintura, Acústica y aislamiento del salón, Aseos: dos bloques y uno adaptado, "&amp;"Instalación eléctrica: cuadro, alumbrado exterior y de emergencia, Climatización del salón, Office del catering: cámara, fregaderos, mesas inox, agua y desagüe, Aparcamiento y caminos: zahorra, señalización e iluminación, Jardinería, "&amp;"paisajismo y riego inicial y Protección contra incendios, señalización de evacuación y accesibilidad), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en "&amp;"la hoja de Supuestos","")</f>
         <v>Al 8% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico y dirección de obra, Adecuación del salón: suelos, cerramientos, carpintería y pintura, Acústica y aislamiento del salón, Aseos: dos bloques y uno adaptado, Instalación eléctrica: cuadro, alumbrado exterior y de emergencia, Climatización del salón, Office del catering: cámara, fregaderos, mesas inox, agua y desagüe, Aparcamiento y caminos: zahorra, señalización e iluminación, Jardinería, paisajismo y riego inicial y Protección contra incendios, señalización de evacuación y accesibilidad), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E28" s="28" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E33" s="28" t="n"/>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="25" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Licencias, tasas, calificación urbanística y prestación compensatoria o canon, Web, fotos, vídeo y marca, Constitución de la SL, Lanzamiento: feria nupcial, puertas abiertas y escaparate premium, Fianza del arrendamiento, Renta de la finca durante la obra ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B31-B36-B37,"0")&amp;" € de los "&amp;TEXT(B31,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Licencias, tasas, calificación urbanística y prestación compensatoria o canon, Web, fotos, vídeo y marca, Constitución de la SL, Lanzamiento: feria nupcial, puertas abiertas y escaparate premium, "&amp;"Fianza del arrendamiento, Renta de la finca durante la obra ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B31-B36-B37,"0")&amp;" € de los "&amp;TEXT(B31,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Licencias, tasas, calificación urbanística y prestación compensatoria o canon, Web, fotos, vídeo y marca, Constitución de la SL, Lanzamiento: feria nupcial, puertas abiertas y escaparate premium, Fianza del arrendamiento, Renta de la finca durante la obra ni Colchón operativo hasta alcanzar el equilibrio. Suman 93129 € de los 311409 € de inversión.</v>
       </c>
       <c r="E38" s="28" t="n"/>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>

--- a/astro-site/public/dl/plan-negocio-finca-eventos-bodas/plan-financiero-finca-eventos-bodas.xlsx
+++ b/astro-site/public/dl/plan-negocio-finca-eventos-bodas/plan-financiero-finca-eventos-bodas.xlsx
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto deben superar las ventas previstas a las del punto de equilibrio. La caída que aguantas antes de entrar en pérdidas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>

--- a/astro-site/public/dl/plan-negocio-finca-eventos-bodas/plan-financiero-finca-eventos-bodas.xlsx
+++ b/astro-site/public/dl/plan-negocio-finca-eventos-bodas/plan-financiero-finca-eventos-bodas.xlsx
@@ -826,7 +826,7 @@
         <v>44.769999999999996</v>
       </c>
       <c r="C9" t="str">
-        <f>IFERROR("Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: "&amp;TEXT(SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)*100,"0")&amp;" %. La finca factura el espacio, los servicios y el canon al 21 %, el tipo general; el menú y la barra los factura el catering a los novios, al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992), y no entran en este libro. Aquí va redondeado. Compáralo con el rango del sector, que va con IVA.","")</f>
+        <f>IFERROR("Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: "&amp;TEXT(SUMPRODUCT('PyG 3 Años'!$E$10:$E$11,'PyG 3 Años'!$G$10:$G$11)*100,"0")&amp;" %. La finca factura el espacio, los servicios y el canon al 21 %, el tipo general; el menú y la barra los factura el catering a los novios, al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992), y no entran en este libro. Aquí va redondeado. "&amp;"Compáralo con el rango del sector, que va con IVA.","")</f>
         <v>Precio por invitado sin IVA más el IVA medio ponderado de tus líneas de venta: 21 %. La finca factura el espacio, los servicios y el canon al 21 %, el tipo general; el menú y la barra los factura el catering a los novios, al 10 % (art. 91.Uno.2.2.º de la Ley 37/1992), y no entran en este libro. Aquí va redondeado. Compáralo con el rango del sector, que va con IVA.</v>
       </c>
     </row>
@@ -1575,7 +1575,7 @@
       </c>
       <c r="C67" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer sobre lo previsto antes de entrar en pérdidas</t>
+          <t>Cuánto deben superar las ventas previstas a las del equilibrio de caja (costes fijos y cuota del préstamo). La caída que aguantas es algo menor: con un 15 % de holgura, un 13 % de lo previsto</t>
         </is>
       </c>
     </row>
@@ -2251,7 +2251,7 @@
         <v>0.036222488931348266</v>
       </c>
       <c r="D28" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico y dirección de obra, Adecuación del salón: suelos, cerramientos, carpintería y pintura, Acústica y aislamiento del salón, Aseos: dos bloques y uno adaptado, Instalación eléctrica: cuadro, alumbrado exterior y de emergencia, Climatización del salón, Office del catering: cámara, fregaderos, mesas inox, agua y desagüe, Aparcamiento y caminos: zahorra, señalización e iluminación, Jardinería, paisajismo y riego inicial y Protección contra incendios, señalización de evacuación y accesibilidad), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$55,"0%")&amp;" de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico y dirección de obra, Adecuación del salón: suelos, cerramientos, carpintería y pintura, Acústica y aislamiento del salón, Aseos: dos bloques y uno adaptado, "&amp;"Instalación eléctrica: cuadro, alumbrado exterior y de emergencia, Climatización del salón, Office del catering: cámara, fregaderos, mesas inox, agua y desagüe, Aparcamiento y caminos: zahorra, señalización e iluminación, Jardinería, "&amp;"paisajismo y riego inicial y Protección contra incendios, señalización de evacuación y accesibilidad), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en "&amp;"la hoja de Supuestos","")</f>
         <v>Al 8% de las partidas de OBRA Y ACONDICIONAMIENTO de este bloque (Proyecto técnico y dirección de obra, Adecuación del salón: suelos, cerramientos, carpintería y pintura, Acústica y aislamiento del salón, Aseos: dos bloques y uno adaptado, Instalación eléctrica: cuadro, alumbrado exterior y de emergencia, Climatización del salón, Office del catering: cámara, fregaderos, mesas inox, agua y desagüe, Aparcamiento y caminos: zahorra, señalización e iluminación, Jardinería, paisajismo y riego inicial y Protección contra incendios, señalización de evacuación y accesibilidad), no del bloque entero: el resto de partidas del bloque quedan fuera. Un banco no financia una reforma sin colchón: el porcentaje está en la hoja de Supuestos</v>
       </c>
       <c r="E28" s="28" t="inlineStr">
@@ -2348,7 +2348,7 @@
       </c>
       <c r="C33" s="28" t="n"/>
       <c r="D33" s="28" t="str">
-        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
+        <f>IFERROR("Al "&amp;TEXT('0. Supuestos'!$B$41,"0%")&amp;" sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí "&amp;"(21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo","")</f>
         <v>Al 21% sobre las partidas marcadas con «Sí» en la columna de IVA. Las tasas y licencias no están sujetas y los seguros están exentos (art. 20.Uno.16 LIVA). Las tasas y aranceles registrales no llevan IVA; los honorarios de notaría y gestoría sí (21 %, deducible). Se recupera con el modelo 303, pero hay que adelantarlo</v>
       </c>
       <c r="E33" s="28" t="n"/>
@@ -2428,7 +2428,7 @@
       </c>
       <c r="C38" s="28" t="n"/>
       <c r="D38" s="25" t="str">
-        <f>IFERROR("No se amortizan, por no ser inmovilizado, Licencias, tasas, calificación urbanística y prestación compensatoria o canon, Web, fotos, vídeo y marca, Constitución de la SL, Lanzamiento: feria nupcial, puertas abiertas y escaparate premium, Fianza del arrendamiento, Renta de la finca durante la obra ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B31-B36-B37,"0")&amp;" € de los "&amp;TEXT(B31,"0")&amp;" € de inversión.","")</f>
+        <f>IFERROR("No se amortizan, por no ser inmovilizado, Licencias, tasas, calificación urbanística y prestación compensatoria o canon, Web, fotos, vídeo y marca, Constitución de la SL, Lanzamiento: feria nupcial, puertas abiertas y escaparate premium, "&amp;"Fianza del arrendamiento, Renta de la finca durante la obra ni Colchón operativo hasta alcanzar el equilibrio. Suman "&amp;TEXT(B31-B36-B37,"0")&amp;" € de los "&amp;TEXT(B31,"0")&amp;" € de inversión.","")</f>
         <v>No se amortizan, por no ser inmovilizado, Licencias, tasas, calificación urbanística y prestación compensatoria o canon, Web, fotos, vídeo y marca, Constitución de la SL, Lanzamiento: feria nupcial, puertas abiertas y escaparate premium, Fianza del arrendamiento, Renta de la finca durante la obra ni Colchón operativo hasta alcanzar el equilibrio. Suman 93129 € de los 311409 € de inversión.</v>
       </c>
       <c r="E38" s="28" t="n"/>
@@ -4607,7 +4607,7 @@
       </c>
       <c r="E24" s="28" t="inlineStr">
         <is>
-          <t>Cuánto puedes caer antes de no poder pagar los costes fijos y la cuota. El mínimo exigible está en la hoja de Supuestos</t>
+          <t>Cuánto superan tus ventas previstas a las del equilibrio de caja. La caída que aguantas antes de no poder pagar los costes fijos y la cuota es algo menor: con un 25 % de holgura, un 20 %. El mínimo exigible está en la hoja de Supuestos</t>
         </is>
       </c>
       <c r="F24" s="28" t="n"/>
